--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run5/epoch_30/per_file_predictions_epoch_30.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_2048_run5/epoch_30/per_file_predictions_epoch_30.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="523">
   <si>
     <t>Filename</t>
   </si>
@@ -808,772 +808,781 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.8729,0.0358,0.0141,0.0853</t>
-  </si>
-  <si>
-    <t>0.0062,0.0023,0.0015,0.9955</t>
-  </si>
-  <si>
-    <t>0.6360,0.0056,0.0027,0.5233</t>
-  </si>
-  <si>
-    <t>0.0634,0.0103,0.0017,0.9748</t>
-  </si>
-  <si>
-    <t>0.9978,0.0004,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.9902,0.0047,0.0010,0.0021</t>
-  </si>
-  <si>
-    <t>0.9944,0.0023,0.0014,0.0006</t>
-  </si>
-  <si>
-    <t>0.9931,0.0009,0.0005,0.0029</t>
-  </si>
-  <si>
-    <t>0.9867,0.0129,0.0015,0.0010</t>
-  </si>
-  <si>
-    <t>0.9951,0.0033,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.9972,0.0003,0.0001,0.0012</t>
-  </si>
-  <si>
-    <t>0.9962,0.0008,0.0009,0.0007</t>
-  </si>
-  <si>
-    <t>0.8178,0.1107,0.0558,0.0201</t>
-  </si>
-  <si>
-    <t>0.0761,0.0340,0.9006,0.0026</t>
-  </si>
-  <si>
-    <t>0.2227,0.0260,0.7979,0.0003</t>
-  </si>
-  <si>
-    <t>0.0735,0.0720,0.8795,0.0030</t>
-  </si>
-  <si>
-    <t>0.9666,0.0053,0.0451,0.0010</t>
-  </si>
-  <si>
-    <t>0.0024,0.9970,0.0005,0.0004</t>
-  </si>
-  <si>
-    <t>0.0010,0.9973,0.0019,0.0021</t>
-  </si>
-  <si>
-    <t>0.0536,0.9650,0.0023,0.0005</t>
-  </si>
-  <si>
-    <t>0.0072,0.9881,0.0053,0.0025</t>
-  </si>
-  <si>
-    <t>0.0006,0.9980,0.0020,0.0008</t>
-  </si>
-  <si>
-    <t>0.4835,0.0437,0.5136,0.0432</t>
-  </si>
-  <si>
-    <t>0.2691,0.1536,0.6280,0.0112</t>
-  </si>
-  <si>
-    <t>0.0277,0.0050,0.9790,0.0005</t>
-  </si>
-  <si>
-    <t>0.0066,0.0177,0.9607,0.0135</t>
-  </si>
-  <si>
-    <t>0.1072,0.0048,0.9394,0.0010</t>
-  </si>
-  <si>
-    <t>0.0535,0.0209,0.9146,0.0069</t>
-  </si>
-  <si>
-    <t>0.0210,0.0089,0.9701,0.0063</t>
-  </si>
-  <si>
-    <t>0.2094,0.8541,0.0098,0.0032</t>
-  </si>
-  <si>
-    <t>0.6069,0.3729,0.0606,0.0139</t>
-  </si>
-  <si>
-    <t>0.0017,0.0050,0.9936,0.0033</t>
-  </si>
-  <si>
-    <t>0.0179,0.9649,0.0118,0.0003</t>
-  </si>
-  <si>
-    <t>0.9054,0.0548,0.0017,0.0215</t>
-  </si>
-  <si>
-    <t>0.8378,0.0364,0.1204,0.0253</t>
-  </si>
-  <si>
-    <t>0.4127,0.7184,0.0088,0.0022</t>
-  </si>
-  <si>
-    <t>0.0066,0.9837,0.0173,0.0025</t>
-  </si>
-  <si>
-    <t>0.0131,0.6995,0.6832,0.0073</t>
-  </si>
-  <si>
-    <t>0.0325,0.0649,0.9502,0.0080</t>
-  </si>
-  <si>
-    <t>0.0091,0.1360,0.9509,0.0232</t>
-  </si>
-  <si>
-    <t>0.2498,0.0330,0.7345,0.0459</t>
-  </si>
-  <si>
-    <t>0.0053,0.1177,0.9699,0.0025</t>
-  </si>
-  <si>
-    <t>0.0012,0.9936,0.0056,0.0012</t>
-  </si>
-  <si>
-    <t>0.0204,0.0694,0.9251,0.0139</t>
-  </si>
-  <si>
-    <t>0.0148,0.8592,0.0212,0.7159</t>
-  </si>
-  <si>
-    <t>0.0024,0.9846,0.0144,0.0135</t>
-  </si>
-  <si>
-    <t>0.0016,0.9882,0.0297,0.0011</t>
-  </si>
-  <si>
-    <t>0.0005,0.9955,0.0199,0.0018</t>
-  </si>
-  <si>
-    <t>0.0014,0.0443,0.9889,0.0011</t>
-  </si>
-  <si>
-    <t>0.0005,0.5899,0.9888,0.0009</t>
-  </si>
-  <si>
-    <t>0.1713,0.0487,0.8242,0.0075</t>
-  </si>
-  <si>
-    <t>0.0023,0.0010,0.9928,0.0044</t>
-  </si>
-  <si>
-    <t>0.0034,0.0230,0.9838,0.0064</t>
-  </si>
-  <si>
-    <t>0.0039,0.7539,0.8642,0.0021</t>
-  </si>
-  <si>
-    <t>0.9737,0.0290,0.0029,0.0011</t>
-  </si>
-  <si>
-    <t>0.9884,0.0017,0.0028,0.0039</t>
-  </si>
-  <si>
-    <t>0.9900,0.0014,0.0006,0.0045</t>
-  </si>
-  <si>
-    <t>0.0055,0.0182,0.9873,0.0034</t>
-  </si>
-  <si>
-    <t>0.9928,0.0023,0.0007,0.0017</t>
-  </si>
-  <si>
-    <t>0.9943,0.0031,0.0009,0.0007</t>
-  </si>
-  <si>
-    <t>0.9898,0.0069,0.0003,0.0015</t>
-  </si>
-  <si>
-    <t>0.0002,0.9619,0.9741,0.0002</t>
-  </si>
-  <si>
-    <t>0.0032,0.0389,0.9925,0.0009</t>
-  </si>
-  <si>
-    <t>0.0075,0.0552,0.9746,0.0083</t>
-  </si>
-  <si>
-    <t>0.0001,0.9344,0.9915,0.0001</t>
-  </si>
-  <si>
-    <t>0.0029,0.0036,0.9923,0.0013</t>
-  </si>
-  <si>
-    <t>0.0118,0.9798,0.0210,0.0005</t>
-  </si>
-  <si>
-    <t>0.0007,0.9981,0.0016,0.0002</t>
-  </si>
-  <si>
-    <t>0.9554,0.0081,0.0296,0.0061</t>
-  </si>
-  <si>
-    <t>0.8400,0.0909,0.0355,0.0223</t>
-  </si>
-  <si>
-    <t>0.0025,0.0192,0.9909,0.0007</t>
-  </si>
-  <si>
-    <t>0.0004,0.9683,0.8886,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.9867,0.7355,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9994,0.0147,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9631,0.9592,0.0002</t>
-  </si>
-  <si>
-    <t>0.0090,0.0005,0.0077,0.9912</t>
-  </si>
-  <si>
-    <t>0.0010,0.0047,0.0007,0.9988</t>
-  </si>
-  <si>
-    <t>0.0007,0.0041,0.0006,0.9991</t>
-  </si>
-  <si>
-    <t>0.0092,0.0007,0.0018,0.9943</t>
-  </si>
-  <si>
-    <t>0.0025,0.0012,0.0015,0.9978</t>
-  </si>
-  <si>
-    <t>0.0032,0.0076,0.0058,0.9952</t>
-  </si>
-  <si>
-    <t>0.0005,0.9923,0.4256,0.0005</t>
-  </si>
-  <si>
-    <t>0.0003,0.8296,0.9893,0.0003</t>
-  </si>
-  <si>
-    <t>0.0032,0.9793,0.0419,0.0022</t>
-  </si>
-  <si>
-    <t>0.0008,0.8037,0.9739,0.0008</t>
-  </si>
-  <si>
-    <t>0.0001,0.9961,0.2259,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.9722,0.7074,0.0005</t>
-  </si>
-  <si>
-    <t>0.9938,0.0027,0.0005,0.0010</t>
-  </si>
-  <si>
-    <t>0.9945,0.0029,0.0003,0.0007</t>
-  </si>
-  <si>
-    <t>0.9817,0.0303,0.0010,0.0005</t>
-  </si>
-  <si>
-    <t>0.9931,0.0026,0.0004,0.0016</t>
-  </si>
-  <si>
-    <t>0.9925,0.0045,0.0005,0.0012</t>
-  </si>
-  <si>
-    <t>0.9866,0.0079,0.0018,0.0025</t>
-  </si>
-  <si>
-    <t>0.9761,0.0209,0.0039,0.0023</t>
-  </si>
-  <si>
-    <t>0.9827,0.0193,0.0018,0.0009</t>
-  </si>
-  <si>
-    <t>0.9969,0.0003,0.0003,0.0014</t>
-  </si>
-  <si>
-    <t>0.9976,0.0006,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.9944,0.0005,0.0004,0.0025</t>
-  </si>
-  <si>
-    <t>0.9962,0.0002,0.0001,0.0023</t>
-  </si>
-  <si>
-    <t>0.9933,0.0017,0.0007,0.0020</t>
-  </si>
-  <si>
-    <t>0.9913,0.0033,0.0008,0.0018</t>
-  </si>
-  <si>
-    <t>0.9936,0.0020,0.0009,0.0016</t>
-  </si>
-  <si>
-    <t>0.9952,0.0005,0.0002,0.0020</t>
-  </si>
-  <si>
-    <t>0.0171,0.0013,0.9881,0.0009</t>
-  </si>
-  <si>
-    <t>0.0240,0.0329,0.9524,0.0023</t>
-  </si>
-  <si>
-    <t>0.8488,0.0697,0.0311,0.0318</t>
-  </si>
-  <si>
-    <t>0.0587,0.0089,0.9478,0.0029</t>
-  </si>
-  <si>
-    <t>0.0002,0.9986,0.0033,0.0003</t>
-  </si>
-  <si>
-    <t>0.0039,0.9911,0.0091,0.0006</t>
-  </si>
-  <si>
-    <t>0.0283,0.9618,0.0151,0.0051</t>
-  </si>
-  <si>
-    <t>0.0414,0.9642,0.0092,0.0034</t>
-  </si>
-  <si>
-    <t>0.0005,0.9978,0.0043,0.0004</t>
-  </si>
-  <si>
-    <t>0.0002,0.9989,0.0030,0.0002</t>
-  </si>
-  <si>
-    <t>0.6655,0.4604,0.0046,0.0031</t>
-  </si>
-  <si>
-    <t>0.8612,0.0188,0.1501,0.0122</t>
-  </si>
-  <si>
-    <t>0.1068,0.0540,0.8453,0.0165</t>
-  </si>
-  <si>
-    <t>0.7835,0.0388,0.1963,0.0104</t>
-  </si>
-  <si>
-    <t>0.3628,0.0326,0.6826,0.0055</t>
-  </si>
-  <si>
-    <t>0.0301,0.0234,0.0234,0.9691</t>
-  </si>
-  <si>
-    <t>0.0016,0.9918,0.0265,0.0009</t>
-  </si>
-  <si>
-    <t>0.0006,0.9952,0.0208,0.0018</t>
-  </si>
-  <si>
-    <t>0.0004,0.9947,0.0066,0.0140</t>
-  </si>
-  <si>
-    <t>0.0002,0.9752,0.9401,0.0004</t>
-  </si>
-  <si>
-    <t>0.0241,0.9771,0.0031,0.0014</t>
-  </si>
-  <si>
-    <t>0.3890,0.6862,0.0215,0.0050</t>
-  </si>
-  <si>
-    <t>0.3448,0.7372,0.0147,0.0032</t>
-  </si>
-  <si>
-    <t>0.9894,0.0023,0.0000,0.0024</t>
-  </si>
-  <si>
-    <t>0.9894,0.0019,0.0010,0.0038</t>
-  </si>
-  <si>
-    <t>0.9907,0.0011,0.0008,0.0040</t>
-  </si>
-  <si>
-    <t>0.9839,0.0071,0.0061,0.0018</t>
-  </si>
-  <si>
-    <t>0.9971,0.0005,0.0007,0.0005</t>
-  </si>
-  <si>
-    <t>0.9810,0.0105,0.0021,0.0042</t>
-  </si>
-  <si>
-    <t>0.9908,0.0015,0.0018,0.0024</t>
-  </si>
-  <si>
-    <t>0.9915,0.0015,0.0017,0.0020</t>
-  </si>
-  <si>
-    <t>0.0037,0.8165,0.9065,0.0019</t>
-  </si>
-  <si>
-    <t>0.0006,0.9389,0.9369,0.0005</t>
-  </si>
-  <si>
-    <t>0.0105,0.5182,0.8967,0.0031</t>
-  </si>
-  <si>
-    <t>0.0771,0.0924,0.8414,0.0101</t>
-  </si>
-  <si>
-    <t>0.9836,0.0049,0.0026,0.0018</t>
-  </si>
-  <si>
-    <t>0.8751,0.0174,0.1149,0.0085</t>
-  </si>
-  <si>
-    <t>0.4136,0.0101,0.7360,0.0053</t>
-  </si>
-  <si>
-    <t>0.8559,0.0181,0.0831,0.0322</t>
-  </si>
-  <si>
-    <t>0.0300,0.0011,0.0004,0.9911</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,0.0069,0.9993</t>
-  </si>
-  <si>
-    <t>0.0003,0.0046,0.0019,0.9989</t>
-  </si>
-  <si>
-    <t>0.0058,0.0004,0.0023,0.9955</t>
-  </si>
-  <si>
-    <t>0.0002,0.9920,0.5839,0.0002</t>
-  </si>
-  <si>
-    <t>0.9900,0.0018,0.0019,0.0034</t>
-  </si>
-  <si>
-    <t>0.4101,0.6942,0.0071,0.0055</t>
-  </si>
-  <si>
-    <t>0.9859,0.0043,0.0006,0.0051</t>
-  </si>
-  <si>
-    <t>0.6905,0.4612,0.0061,0.0024</t>
-  </si>
-  <si>
-    <t>0.9713,0.0034,0.0095,0.0115</t>
-  </si>
-  <si>
-    <t>0.7024,0.0042,0.0079,0.4462</t>
-  </si>
-  <si>
-    <t>0.9851,0.0041,0.0017,0.0052</t>
-  </si>
-  <si>
-    <t>0.0024,0.0102,0.8355,0.4713</t>
-  </si>
-  <si>
-    <t>0.6691,0.0018,0.0015,0.5640</t>
-  </si>
-  <si>
-    <t>0.9543,0.0049,0.0042,0.0310</t>
-  </si>
-  <si>
-    <t>0.2144,0.8465,0.0022,0.0107</t>
-  </si>
-  <si>
-    <t>0.8716,0.0866,0.0023,0.0213</t>
-  </si>
-  <si>
-    <t>0.9489,0.0402,0.0093,0.0020</t>
-  </si>
-  <si>
-    <t>0.1922,0.7855,0.0105,0.0248</t>
-  </si>
-  <si>
-    <t>0.9397,0.0232,0.0409,0.0042</t>
-  </si>
-  <si>
-    <t>0.8376,0.1361,0.0167,0.0170</t>
-  </si>
-  <si>
-    <t>0.9944,0.0007,0.0005,0.0022</t>
-  </si>
-  <si>
-    <t>0.9860,0.0019,0.0025,0.0053</t>
-  </si>
-  <si>
-    <t>0.9900,0.0021,0.0011,0.0029</t>
-  </si>
-  <si>
-    <t>0.9829,0.0006,0.0018,0.0112</t>
-  </si>
-  <si>
-    <t>0.9898,0.0029,0.0005,0.0030</t>
-  </si>
-  <si>
-    <t>0.9852,0.0043,0.0055,0.0026</t>
-  </si>
-  <si>
-    <t>0.9929,0.0009,0.0016,0.0022</t>
-  </si>
-  <si>
-    <t>0.9899,0.0010,0.0004,0.0053</t>
-  </si>
-  <si>
-    <t>0.6436,0.4041,0.0009,0.0037</t>
-  </si>
-  <si>
-    <t>0.8169,0.2439,0.0071,0.0074</t>
-  </si>
-  <si>
-    <t>0.8248,0.2664,0.0028,0.0024</t>
-  </si>
-  <si>
-    <t>0.7763,0.0630,0.2180,0.0122</t>
-  </si>
-  <si>
-    <t>0.9744,0.0208,0.0015,0.0025</t>
-  </si>
-  <si>
-    <t>0.9880,0.0083,0.0005,0.0018</t>
-  </si>
-  <si>
-    <t>0.9913,0.0062,0.0015,0.0007</t>
-  </si>
-  <si>
-    <t>0.9857,0.0042,0.0016,0.0040</t>
-  </si>
-  <si>
-    <t>0.0007,0.0110,0.9979,0.0002</t>
-  </si>
-  <si>
-    <t>0.9308,0.0250,0.0613,0.0026</t>
-  </si>
-  <si>
-    <t>0.0082,0.0135,0.9831,0.0013</t>
-  </si>
-  <si>
-    <t>0.0031,0.3816,0.9687,0.0020</t>
-  </si>
-  <si>
-    <t>0.0024,0.0025,0.9931,0.0018</t>
-  </si>
-  <si>
-    <t>0.0009,0.1434,0.9946,0.0002</t>
-  </si>
-  <si>
-    <t>0.0086,0.0210,0.9745,0.0024</t>
-  </si>
-  <si>
-    <t>0.0042,0.0132,0.9849,0.0027</t>
-  </si>
-  <si>
-    <t>0.0010,0.0103,0.9924,0.0044</t>
-  </si>
-  <si>
-    <t>0.6022,0.0471,0.3835,0.0214</t>
-  </si>
-  <si>
-    <t>0.1614,0.0127,0.8764,0.0027</t>
-  </si>
-  <si>
-    <t>0.3964,0.1478,0.5035,0.0219</t>
-  </si>
-  <si>
-    <t>0.1129,0.7370,0.1554,0.0052</t>
-  </si>
-  <si>
-    <t>0.1210,0.5565,0.3158,0.0028</t>
-  </si>
-  <si>
-    <t>0.7199,0.0348,0.2920,0.0028</t>
-  </si>
-  <si>
-    <t>0.4102,0.0240,0.6227,0.0102</t>
-  </si>
-  <si>
-    <t>0.6236,0.0909,0.3060,0.0484</t>
-  </si>
-  <si>
-    <t>0.0712,0.9617,0.0025,0.0006</t>
-  </si>
-  <si>
-    <t>0.0096,0.9922,0.0010,0.0002</t>
-  </si>
-  <si>
-    <t>0.4007,0.8155,0.0013,0.0015</t>
-  </si>
-  <si>
-    <t>0.8746,0.2453,0.0010,0.0014</t>
-  </si>
-  <si>
-    <t>0.4841,0.7516,0.0025,0.0006</t>
-  </si>
-  <si>
-    <t>0.7136,0.2039,0.0797,0.0190</t>
-  </si>
-  <si>
-    <t>0.8583,0.0211,0.1845,0.0043</t>
-  </si>
-  <si>
-    <t>0.8688,0.0125,0.0946,0.0211</t>
-  </si>
-  <si>
-    <t>0.7238,0.1794,0.0981,0.0459</t>
-  </si>
-  <si>
-    <t>0.8392,0.0327,0.0740,0.0430</t>
-  </si>
-  <si>
-    <t>0.0049,0.0081,0.9795,0.0121</t>
-  </si>
-  <si>
-    <t>0.0029,0.7601,0.8031,0.0045</t>
-  </si>
-  <si>
-    <t>0.0013,0.5126,0.9803,0.0013</t>
-  </si>
-  <si>
-    <t>0.0094,0.0254,0.9625,0.0146</t>
-  </si>
-  <si>
-    <t>0.0021,0.0788,0.9728,0.0095</t>
-  </si>
-  <si>
-    <t>0.9918,0.0017,0.0003,0.0028</t>
-  </si>
-  <si>
-    <t>0.9902,0.0036,0.0012,0.0020</t>
-  </si>
-  <si>
-    <t>0.9880,0.0081,0.0028,0.0013</t>
-  </si>
-  <si>
-    <t>0.9736,0.0350,0.0019,0.0012</t>
-  </si>
-  <si>
-    <t>0.9855,0.0074,0.0039,0.0016</t>
-  </si>
-  <si>
-    <t>0.9721,0.0270,0.0025,0.0032</t>
-  </si>
-  <si>
-    <t>0.9817,0.0088,0.0021,0.0047</t>
-  </si>
-  <si>
-    <t>0.9833,0.0046,0.0029,0.0041</t>
-  </si>
-  <si>
-    <t>0.0031,0.0058,0.9863,0.0110</t>
-  </si>
-  <si>
-    <t>0.2871,0.0427,0.6334,0.0758</t>
-  </si>
-  <si>
-    <t>0.8752,0.0030,0.0139,0.0951</t>
-  </si>
-  <si>
-    <t>0.0145,0.0104,0.9769,0.0017</t>
-  </si>
-  <si>
-    <t>0.0006,0.0019,0.9975,0.0008</t>
-  </si>
-  <si>
-    <t>0.0036,0.7503,0.7062,0.0023</t>
-  </si>
-  <si>
-    <t>0.0062,0.0049,0.9918,0.0010</t>
-  </si>
-  <si>
-    <t>0.0542,0.0207,0.9357,0.0024</t>
-  </si>
-  <si>
-    <t>0.0011,0.0754,0.9941,0.0012</t>
-  </si>
-  <si>
-    <t>0.0065,0.0823,0.9554,0.0151</t>
-  </si>
-  <si>
-    <t>0.0487,0.0367,0.9047,0.0119</t>
-  </si>
-  <si>
-    <t>0.4368,0.0286,0.4651,0.0775</t>
-  </si>
-  <si>
-    <t>0.8224,0.0189,0.2295,0.0035</t>
-  </si>
-  <si>
-    <t>0.8664,0.0475,0.0758,0.0146</t>
-  </si>
-  <si>
-    <t>0.9258,0.1447,0.0028,0.0009</t>
-  </si>
-  <si>
-    <t>0.9723,0.0440,0.0016,0.0006</t>
-  </si>
-  <si>
-    <t>0.9917,0.0047,0.0017,0.0008</t>
-  </si>
-  <si>
-    <t>0.9741,0.0221,0.0072,0.0012</t>
-  </si>
-  <si>
-    <t>0.9910,0.0032,0.0008,0.0022</t>
-  </si>
-  <si>
-    <t>0.9519,0.1217,0.0009,0.0003</t>
-  </si>
-  <si>
-    <t>0.9813,0.0238,0.0017,0.0006</t>
-  </si>
-  <si>
-    <t>0.9897,0.0046,0.0006,0.0027</t>
-  </si>
-  <si>
-    <t>0.0272,0.4932,0.6246,0.0061</t>
-  </si>
-  <si>
-    <t>0.0023,0.3577,0.9758,0.0027</t>
-  </si>
-  <si>
-    <t>0.0085,0.2623,0.9437,0.0031</t>
-  </si>
-  <si>
-    <t>0.0339,0.0345,0.9162,0.0116</t>
-  </si>
-  <si>
-    <t>0.0022,0.0017,0.9928,0.0031</t>
-  </si>
-  <si>
-    <t>0.0277,0.0250,0.8358,0.2622</t>
-  </si>
-  <si>
-    <t>0.0095,0.0069,0.9732,0.0084</t>
-  </si>
-  <si>
-    <t>0.0235,0.0201,0.9255,0.0676</t>
-  </si>
-  <si>
-    <t>0.5243,0.0016,0.0028,0.7204</t>
-  </si>
-  <si>
-    <t>0.0317,0.0383,0.0023,0.9780</t>
-  </si>
-  <si>
-    <t>0.0138,0.0145,0.0028,0.9890</t>
-  </si>
-  <si>
-    <t>0.0009,0.0003,0.0064,0.9977</t>
-  </si>
-  <si>
-    <t>0.0038,0.0013,0.0027,0.9962</t>
-  </si>
-  <si>
-    <t>0.6154,0.0303,0.0025,0.3497</t>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.9475,0.0059,0.0060,0.0425</t>
+  </si>
+  <si>
+    <t>0.0040,0.0034,0.0019,0.9964</t>
+  </si>
+  <si>
+    <t>0.5973,0.0042,0.0013,0.6098</t>
+  </si>
+  <si>
+    <t>0.0122,0.0179,0.0005,0.9923</t>
+  </si>
+  <si>
+    <t>0.9946,0.0015,0.0013,0.0010</t>
+  </si>
+  <si>
+    <t>0.9906,0.0039,0.0004,0.0018</t>
+  </si>
+  <si>
+    <t>0.9954,0.0006,0.0002,0.0016</t>
+  </si>
+  <si>
+    <t>0.9887,0.0009,0.0028,0.0038</t>
+  </si>
+  <si>
+    <t>0.9701,0.0358,0.0063,0.0013</t>
+  </si>
+  <si>
+    <t>0.9909,0.0071,0.0007,0.0010</t>
+  </si>
+  <si>
+    <t>0.9959,0.0007,0.0004,0.0011</t>
+  </si>
+  <si>
+    <t>0.9940,0.0008,0.0003,0.0024</t>
+  </si>
+  <si>
+    <t>0.7950,0.0999,0.0743,0.0265</t>
+  </si>
+  <si>
+    <t>0.0421,0.0418,0.9270,0.0036</t>
+  </si>
+  <si>
+    <t>0.2669,0.1503,0.5638,0.0010</t>
+  </si>
+  <si>
+    <t>0.1103,0.0651,0.8107,0.0060</t>
+  </si>
+  <si>
+    <t>0.8512,0.0752,0.1066,0.0097</t>
+  </si>
+  <si>
+    <t>0.0010,0.9980,0.0020,0.0004</t>
+  </si>
+  <si>
+    <t>0.0009,0.9977,0.0016,0.0006</t>
+  </si>
+  <si>
+    <t>0.0272,0.9797,0.0011,0.0005</t>
+  </si>
+  <si>
+    <t>0.0018,0.9959,0.0024,0.0025</t>
+  </si>
+  <si>
+    <t>0.0012,0.9972,0.0026,0.0004</t>
+  </si>
+  <si>
+    <t>0.5587,0.0461,0.4065,0.0655</t>
+  </si>
+  <si>
+    <t>0.7441,0.1038,0.1713,0.0257</t>
+  </si>
+  <si>
+    <t>0.0089,0.0065,0.9835,0.0020</t>
+  </si>
+  <si>
+    <t>0.0210,0.0139,0.9401,0.0307</t>
+  </si>
+  <si>
+    <t>0.1976,0.0074,0.9006,0.0006</t>
+  </si>
+  <si>
+    <t>0.1499,0.0148,0.8569,0.0147</t>
+  </si>
+  <si>
+    <t>0.0053,0.0012,0.9928,0.0009</t>
+  </si>
+  <si>
+    <t>0.1200,0.9310,0.0029,0.0036</t>
+  </si>
+  <si>
+    <t>0.4692,0.5197,0.0828,0.0120</t>
+  </si>
+  <si>
+    <t>0.0004,0.0126,0.9968,0.0017</t>
+  </si>
+  <si>
+    <t>0.0082,0.9901,0.0018,0.0004</t>
+  </si>
+  <si>
+    <t>0.9600,0.0242,0.0023,0.0060</t>
+  </si>
+  <si>
+    <t>0.9399,0.0282,0.0138,0.0087</t>
+  </si>
+  <si>
+    <t>0.4079,0.7216,0.0083,0.0036</t>
+  </si>
+  <si>
+    <t>0.0115,0.9599,0.0766,0.0126</t>
+  </si>
+  <si>
+    <t>0.0052,0.9647,0.1587,0.0034</t>
+  </si>
+  <si>
+    <t>0.0065,0.0878,0.9665,0.0109</t>
+  </si>
+  <si>
+    <t>0.0070,0.0372,0.9761,0.0071</t>
+  </si>
+  <si>
+    <t>0.0271,0.1314,0.8804,0.0903</t>
+  </si>
+  <si>
+    <t>0.0251,0.3307,0.8749,0.0019</t>
+  </si>
+  <si>
+    <t>0.0058,0.9812,0.0127,0.0010</t>
+  </si>
+  <si>
+    <t>0.0046,0.0476,0.9648,0.0231</t>
+  </si>
+  <si>
+    <t>0.0084,0.6763,0.0118,0.8274</t>
+  </si>
+  <si>
+    <t>0.0010,0.9928,0.0148,0.0028</t>
+  </si>
+  <si>
+    <t>0.0019,0.9835,0.1464,0.0027</t>
+  </si>
+  <si>
+    <t>0.0006,0.9909,0.1522,0.0030</t>
+  </si>
+  <si>
+    <t>0.0017,0.1571,0.9830,0.0022</t>
+  </si>
+  <si>
+    <t>0.0007,0.1097,0.9880,0.0028</t>
+  </si>
+  <si>
+    <t>0.0327,0.0058,0.9652,0.0040</t>
+  </si>
+  <si>
+    <t>0.0053,0.0034,0.9825,0.0094</t>
+  </si>
+  <si>
+    <t>0.0092,0.1185,0.9700,0.0049</t>
+  </si>
+  <si>
+    <t>0.0066,0.7833,0.8346,0.0042</t>
+  </si>
+  <si>
+    <t>0.9738,0.0352,0.0008,0.0016</t>
+  </si>
+  <si>
+    <t>0.9856,0.0040,0.0030,0.0034</t>
+  </si>
+  <si>
+    <t>0.9875,0.0034,0.0044,0.0018</t>
+  </si>
+  <si>
+    <t>0.0017,0.0198,0.9926,0.0038</t>
+  </si>
+  <si>
+    <t>0.9874,0.0043,0.0027,0.0023</t>
+  </si>
+  <si>
+    <t>0.9941,0.0024,0.0011,0.0006</t>
+  </si>
+  <si>
+    <t>0.9534,0.0813,0.0010,0.0018</t>
+  </si>
+  <si>
+    <t>0.0001,0.9359,0.9945,0.0001</t>
+  </si>
+  <si>
+    <t>0.0021,0.0091,0.9925,0.0031</t>
+  </si>
+  <si>
+    <t>0.0199,0.0080,0.9766,0.0021</t>
+  </si>
+  <si>
+    <t>0.0001,0.9388,0.9855,0.0001</t>
+  </si>
+  <si>
+    <t>0.0017,0.0014,0.9947,0.0025</t>
+  </si>
+  <si>
+    <t>0.1073,0.9238,0.0045,0.0015</t>
+  </si>
+  <si>
+    <t>0.0005,0.9984,0.0020,0.0002</t>
+  </si>
+  <si>
+    <t>0.9663,0.0124,0.0072,0.0072</t>
+  </si>
+  <si>
+    <t>0.9376,0.0247,0.0244,0.0069</t>
+  </si>
+  <si>
+    <t>0.0077,0.0108,0.9837,0.0020</t>
+  </si>
+  <si>
+    <t>0.0001,0.9554,0.9740,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9890,0.8774,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9993,0.0163,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.9974,0.1432,0.0002</t>
+  </si>
+  <si>
+    <t>0.0230,0.0025,0.0167,0.9779</t>
+  </si>
+  <si>
+    <t>0.0013,0.0026,0.0011,0.9984</t>
+  </si>
+  <si>
+    <t>0.0026,0.0111,0.0005,0.9981</t>
+  </si>
+  <si>
+    <t>0.0072,0.0008,0.0027,0.9945</t>
+  </si>
+  <si>
+    <t>0.0069,0.0115,0.0049,0.9924</t>
+  </si>
+  <si>
+    <t>0.0012,0.0104,0.0164,0.9951</t>
+  </si>
+  <si>
+    <t>0.0002,0.9846,0.9142,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.8233,0.9940,0.0001</t>
+  </si>
+  <si>
+    <t>0.0018,0.9333,0.7252,0.0025</t>
+  </si>
+  <si>
+    <t>0.0013,0.8328,0.9541,0.0011</t>
+  </si>
+  <si>
+    <t>0.0003,0.9831,0.9056,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.9942,0.2930,0.0004</t>
+  </si>
+  <si>
+    <t>0.9954,0.0015,0.0003,0.0009</t>
+  </si>
+  <si>
+    <t>0.9903,0.0130,0.0008,0.0003</t>
+  </si>
+  <si>
+    <t>0.9918,0.0068,0.0007,0.0006</t>
+  </si>
+  <si>
+    <t>0.9921,0.0024,0.0003,0.0020</t>
+  </si>
+  <si>
+    <t>0.9930,0.0046,0.0003,0.0010</t>
+  </si>
+  <si>
+    <t>0.9749,0.0324,0.0030,0.0015</t>
+  </si>
+  <si>
+    <t>0.9775,0.0203,0.0046,0.0020</t>
+  </si>
+  <si>
+    <t>0.9846,0.0092,0.0012,0.0023</t>
+  </si>
+  <si>
+    <t>0.9923,0.0004,0.0004,0.0058</t>
+  </si>
+  <si>
+    <t>0.9987,0.0003,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9964,0.0002,0.0001,0.0020</t>
+  </si>
+  <si>
+    <t>0.9984,0.0002,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9965,0.0002,0.0001,0.0023</t>
+  </si>
+  <si>
+    <t>0.9924,0.0023,0.0007,0.0021</t>
+  </si>
+  <si>
+    <t>0.9941,0.0014,0.0020,0.0014</t>
+  </si>
+  <si>
+    <t>0.9946,0.0005,0.0006,0.0021</t>
+  </si>
+  <si>
+    <t>0.0011,0.0008,0.9966,0.0016</t>
+  </si>
+  <si>
+    <t>0.0577,0.1194,0.8566,0.0119</t>
+  </si>
+  <si>
+    <t>0.9480,0.0135,0.0149,0.0086</t>
+  </si>
+  <si>
+    <t>0.3007,0.0124,0.8088,0.0012</t>
+  </si>
+  <si>
+    <t>0.0005,0.9977,0.0059,0.0003</t>
+  </si>
+  <si>
+    <t>0.0027,0.9943,0.0038,0.0003</t>
+  </si>
+  <si>
+    <t>0.0126,0.9801,0.0138,0.0016</t>
+  </si>
+  <si>
+    <t>0.0394,0.9647,0.0064,0.0016</t>
+  </si>
+  <si>
+    <t>0.0019,0.9945,0.0076,0.0009</t>
+  </si>
+  <si>
+    <t>0.0006,0.9974,0.0065,0.0004</t>
+  </si>
+  <si>
+    <t>0.2188,0.8543,0.0065,0.0008</t>
+  </si>
+  <si>
+    <t>0.7106,0.1628,0.1114,0.0527</t>
+  </si>
+  <si>
+    <t>0.4295,0.0685,0.5241,0.0161</t>
+  </si>
+  <si>
+    <t>0.6897,0.0291,0.2945,0.0181</t>
+  </si>
+  <si>
+    <t>0.9132,0.0144,0.1082,0.0019</t>
+  </si>
+  <si>
+    <t>0.0376,0.0460,0.0117,0.9636</t>
+  </si>
+  <si>
+    <t>0.0003,0.9977,0.0145,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.9970,0.0073,0.0010</t>
+  </si>
+  <si>
+    <t>0.0001,0.9971,0.0018,0.0416</t>
+  </si>
+  <si>
+    <t>0.0001,0.9949,0.6385,0.0003</t>
+  </si>
+  <si>
+    <t>0.0058,0.9909,0.0020,0.0006</t>
+  </si>
+  <si>
+    <t>0.4412,0.6395,0.0082,0.0111</t>
+  </si>
+  <si>
+    <t>0.3512,0.7605,0.0098,0.0026</t>
+  </si>
+  <si>
+    <t>0.9936,0.0021,0.0001,0.0013</t>
+  </si>
+  <si>
+    <t>0.9863,0.0023,0.0015,0.0060</t>
+  </si>
+  <si>
+    <t>0.9887,0.0016,0.0010,0.0043</t>
+  </si>
+  <si>
+    <t>0.9911,0.0022,0.0028,0.0015</t>
+  </si>
+  <si>
+    <t>0.9945,0.0010,0.0007,0.0015</t>
+  </si>
+  <si>
+    <t>0.9893,0.0032,0.0006,0.0030</t>
+  </si>
+  <si>
+    <t>0.9892,0.0012,0.0013,0.0047</t>
+  </si>
+  <si>
+    <t>0.9930,0.0005,0.0006,0.0035</t>
+  </si>
+  <si>
+    <t>0.0064,0.8461,0.7090,0.0022</t>
+  </si>
+  <si>
+    <t>0.0011,0.9169,0.9252,0.0007</t>
+  </si>
+  <si>
+    <t>0.0051,0.1963,0.9477,0.0010</t>
+  </si>
+  <si>
+    <t>0.0389,0.2403,0.7798,0.0057</t>
+  </si>
+  <si>
+    <t>0.9745,0.0055,0.0089,0.0029</t>
+  </si>
+  <si>
+    <t>0.5993,0.0363,0.4224,0.0141</t>
+  </si>
+  <si>
+    <t>0.5675,0.0047,0.5975,0.0043</t>
+  </si>
+  <si>
+    <t>0.8089,0.0907,0.0585,0.0254</t>
+  </si>
+  <si>
+    <t>0.0162,0.0056,0.0030,0.9904</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.0173,0.9985</t>
+  </si>
+  <si>
+    <t>0.0011,0.0321,0.0015,0.9974</t>
+  </si>
+  <si>
+    <t>0.0008,0.0008,0.0008,0.9991</t>
+  </si>
+  <si>
+    <t>0.0002,0.9926,0.5804,0.0001</t>
+  </si>
+  <si>
+    <t>0.9851,0.0092,0.0016,0.0027</t>
+  </si>
+  <si>
+    <t>0.1405,0.8974,0.0040,0.0063</t>
+  </si>
+  <si>
+    <t>0.9886,0.0014,0.0012,0.0053</t>
+  </si>
+  <si>
+    <t>0.2917,0.8320,0.0040,0.0024</t>
+  </si>
+  <si>
+    <t>0.9666,0.0025,0.0179,0.0078</t>
+  </si>
+  <si>
+    <t>0.8980,0.0200,0.0188,0.0630</t>
+  </si>
+  <si>
+    <t>0.9690,0.0083,0.0073,0.0117</t>
+  </si>
+  <si>
+    <t>0.0042,0.0484,0.7076,0.4883</t>
+  </si>
+  <si>
+    <t>0.5059,0.0007,0.0012,0.7931</t>
+  </si>
+  <si>
+    <t>0.8857,0.0042,0.0045,0.1260</t>
+  </si>
+  <si>
+    <t>0.1141,0.9042,0.0061,0.0085</t>
+  </si>
+  <si>
+    <t>0.9652,0.0195,0.0106,0.0026</t>
+  </si>
+  <si>
+    <t>0.9779,0.0171,0.0036,0.0012</t>
+  </si>
+  <si>
+    <t>0.2049,0.7905,0.0233,0.0214</t>
+  </si>
+  <si>
+    <t>0.9057,0.0882,0.0196,0.0028</t>
+  </si>
+  <si>
+    <t>0.7680,0.2297,0.0055,0.0233</t>
+  </si>
+  <si>
+    <t>0.9888,0.0016,0.0012,0.0042</t>
+  </si>
+  <si>
+    <t>0.9821,0.0065,0.0015,0.0048</t>
+  </si>
+  <si>
+    <t>0.9854,0.0024,0.0044,0.0041</t>
+  </si>
+  <si>
+    <t>0.9810,0.0008,0.0047,0.0085</t>
+  </si>
+  <si>
+    <t>0.9925,0.0012,0.0003,0.0028</t>
+  </si>
+  <si>
+    <t>0.9875,0.0031,0.0056,0.0016</t>
+  </si>
+  <si>
+    <t>0.9945,0.0006,0.0005,0.0023</t>
+  </si>
+  <si>
+    <t>0.9924,0.0003,0.0003,0.0056</t>
+  </si>
+  <si>
+    <t>0.8482,0.1694,0.0017,0.0058</t>
+  </si>
+  <si>
+    <t>0.6031,0.5543,0.0066,0.0018</t>
+  </si>
+  <si>
+    <t>0.4443,0.6582,0.0021,0.0049</t>
+  </si>
+  <si>
+    <t>0.1022,0.2159,0.7920,0.0019</t>
+  </si>
+  <si>
+    <t>0.9861,0.0078,0.0007,0.0016</t>
+  </si>
+  <si>
+    <t>0.9631,0.0287,0.0008,0.0050</t>
+  </si>
+  <si>
+    <t>0.9787,0.0146,0.0012,0.0027</t>
+  </si>
+  <si>
+    <t>0.9915,0.0031,0.0008,0.0015</t>
+  </si>
+  <si>
+    <t>0.0016,0.0098,0.9969,0.0002</t>
+  </si>
+  <si>
+    <t>0.9721,0.0118,0.0107,0.0039</t>
+  </si>
+  <si>
+    <t>0.0055,0.0095,0.9865,0.0014</t>
+  </si>
+  <si>
+    <t>0.0069,0.6847,0.8640,0.0023</t>
+  </si>
+  <si>
+    <t>0.0065,0.0166,0.9755,0.0050</t>
+  </si>
+  <si>
+    <t>0.0020,0.3518,0.9823,0.0009</t>
+  </si>
+  <si>
+    <t>0.0022,0.0086,0.9926,0.0004</t>
+  </si>
+  <si>
+    <t>0.0159,0.0135,0.9819,0.0005</t>
+  </si>
+  <si>
+    <t>0.0017,0.0587,0.9866,0.0037</t>
+  </si>
+  <si>
+    <t>0.0894,0.0318,0.8791,0.0120</t>
+  </si>
+  <si>
+    <t>0.8825,0.0090,0.1681,0.0037</t>
+  </si>
+  <si>
+    <t>0.2458,0.1386,0.5397,0.0063</t>
+  </si>
+  <si>
+    <t>0.5380,0.1340,0.2578,0.0025</t>
+  </si>
+  <si>
+    <t>0.2067,0.2097,0.6446,0.0047</t>
+  </si>
+  <si>
+    <t>0.8432,0.0149,0.2266,0.0012</t>
+  </si>
+  <si>
+    <t>0.7352,0.0298,0.2401,0.0394</t>
+  </si>
+  <si>
+    <t>0.3249,0.0237,0.7005,0.0150</t>
+  </si>
+  <si>
+    <t>0.0202,0.9813,0.0027,0.0004</t>
+  </si>
+  <si>
+    <t>0.1360,0.9387,0.0019,0.0004</t>
+  </si>
+  <si>
+    <t>0.9124,0.1769,0.0029,0.0007</t>
+  </si>
+  <si>
+    <t>0.9582,0.0708,0.0029,0.0012</t>
+  </si>
+  <si>
+    <t>0.8782,0.2542,0.0017,0.0015</t>
+  </si>
+  <si>
+    <t>0.6287,0.2001,0.1524,0.0371</t>
+  </si>
+  <si>
+    <t>0.9214,0.0100,0.0944,0.0025</t>
+  </si>
+  <si>
+    <t>0.8531,0.0361,0.0370,0.0397</t>
+  </si>
+  <si>
+    <t>0.7376,0.1666,0.0504,0.0591</t>
+  </si>
+  <si>
+    <t>0.4042,0.0259,0.5867,0.0386</t>
+  </si>
+  <si>
+    <t>0.0096,0.0071,0.9722,0.0143</t>
+  </si>
+  <si>
+    <t>0.0024,0.3914,0.9047,0.0084</t>
+  </si>
+  <si>
+    <t>0.0036,0.1288,0.9632,0.0088</t>
+  </si>
+  <si>
+    <t>0.0371,0.0612,0.9099,0.0092</t>
+  </si>
+  <si>
+    <t>0.0017,0.0522,0.9831,0.0031</t>
+  </si>
+  <si>
+    <t>0.9913,0.0012,0.0003,0.0038</t>
+  </si>
+  <si>
+    <t>0.9911,0.0024,0.0013,0.0023</t>
+  </si>
+  <si>
+    <t>0.9893,0.0077,0.0010,0.0013</t>
+  </si>
+  <si>
+    <t>0.9749,0.0381,0.0025,0.0014</t>
+  </si>
+  <si>
+    <t>0.9792,0.0156,0.0017,0.0022</t>
+  </si>
+  <si>
+    <t>0.9882,0.0047,0.0006,0.0021</t>
+  </si>
+  <si>
+    <t>0.9908,0.0019,0.0003,0.0035</t>
+  </si>
+  <si>
+    <t>0.9826,0.0018,0.0011,0.0112</t>
+  </si>
+  <si>
+    <t>0.0045,0.0057,0.9801,0.0242</t>
+  </si>
+  <si>
+    <t>0.1200,0.1128,0.7508,0.0051</t>
+  </si>
+  <si>
+    <t>0.9489,0.0095,0.0151,0.0205</t>
+  </si>
+  <si>
+    <t>0.0084,0.0096,0.9855,0.0005</t>
+  </si>
+  <si>
+    <t>0.0015,0.0017,0.9947,0.0022</t>
+  </si>
+  <si>
+    <t>0.0011,0.3539,0.9739,0.0013</t>
+  </si>
+  <si>
+    <t>0.0011,0.0017,0.9967,0.0019</t>
+  </si>
+  <si>
+    <t>0.0093,0.0294,0.9706,0.0021</t>
+  </si>
+  <si>
+    <t>0.0010,0.0973,0.9941,0.0004</t>
+  </si>
+  <si>
+    <t>0.0162,0.2867,0.8396,0.0228</t>
+  </si>
+  <si>
+    <t>0.0118,0.0914,0.9130,0.0092</t>
+  </si>
+  <si>
+    <t>0.4225,0.0184,0.6097,0.0148</t>
+  </si>
+  <si>
+    <t>0.6777,0.0149,0.4609,0.0027</t>
+  </si>
+  <si>
+    <t>0.9789,0.0051,0.0048,0.0021</t>
+  </si>
+  <si>
+    <t>0.9809,0.0230,0.0014,0.0011</t>
+  </si>
+  <si>
+    <t>0.9879,0.0111,0.0020,0.0006</t>
+  </si>
+  <si>
+    <t>0.9911,0.0080,0.0009,0.0006</t>
+  </si>
+  <si>
+    <t>0.9799,0.0236,0.0011,0.0010</t>
+  </si>
+  <si>
+    <t>0.9877,0.0015,0.0002,0.0078</t>
+  </si>
+  <si>
+    <t>0.9861,0.0158,0.0012,0.0006</t>
+  </si>
+  <si>
+    <t>0.9928,0.0028,0.0008,0.0013</t>
+  </si>
+  <si>
+    <t>0.9877,0.0111,0.0009,0.0012</t>
+  </si>
+  <si>
+    <t>0.1091,0.3323,0.5173,0.0027</t>
+  </si>
+  <si>
+    <t>0.0026,0.1953,0.9840,0.0013</t>
+  </si>
+  <si>
+    <t>0.0070,0.3166,0.9424,0.0053</t>
+  </si>
+  <si>
+    <t>0.0095,0.0150,0.9673,0.0066</t>
+  </si>
+  <si>
+    <t>0.0023,0.0058,0.9889,0.0048</t>
+  </si>
+  <si>
+    <t>0.0270,0.0275,0.8866,0.1519</t>
+  </si>
+  <si>
+    <t>0.0701,0.0220,0.7585,0.2327</t>
+  </si>
+  <si>
+    <t>0.0032,0.0045,0.9577,0.1277</t>
+  </si>
+  <si>
+    <t>0.8927,0.0031,0.0007,0.1747</t>
+  </si>
+  <si>
+    <t>0.0042,0.0827,0.0010,0.9923</t>
+  </si>
+  <si>
+    <t>0.0665,0.0029,0.0010,0.9785</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.0010,0.9997</t>
+  </si>
+  <si>
+    <t>0.0012,0.0044,0.0010,0.9987</t>
+  </si>
+  <si>
+    <t>0.6577,0.0313,0.0033,0.3212</t>
   </si>
 </sst>
 </file>
@@ -1959,7 +1968,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1973,7 +1982,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,10 +1993,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2001,7 +2010,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2015,7 +2024,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2029,7 +2038,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2043,7 +2052,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2057,7 +2066,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2071,7 +2080,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2085,7 +2094,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2099,7 +2108,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2113,7 +2122,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2127,7 +2136,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2141,7 +2150,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2155,7 +2164,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2169,7 +2178,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2183,7 +2192,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2197,7 +2206,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2211,7 +2220,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2225,7 +2234,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2239,7 +2248,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2253,7 +2262,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,10 +2273,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,10 +2287,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2295,7 +2304,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2309,7 +2318,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2323,7 +2332,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2337,7 +2346,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2351,7 +2360,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2365,7 +2374,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,10 +2385,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2393,7 +2402,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2407,7 +2416,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,7 +2430,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2435,7 +2444,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2449,7 +2458,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2463,7 +2472,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,10 +2483,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2491,7 +2500,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2505,7 +2514,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2519,7 +2528,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2533,7 +2542,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2547,7 +2556,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2561,7 +2570,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,10 +2581,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2589,7 +2598,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2603,7 +2612,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2617,7 +2626,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2631,7 +2640,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,10 +2651,10 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2659,7 +2668,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2673,7 +2682,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2687,7 +2696,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2701,7 +2710,7 @@
         <v>263</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2715,7 +2724,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2729,7 +2738,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2743,7 +2752,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2757,7 +2766,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2771,7 +2780,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2785,7 +2794,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2799,7 +2808,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2813,7 +2822,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2827,7 +2836,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2841,7 +2850,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2855,7 +2864,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2869,7 +2878,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2883,7 +2892,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2897,7 +2906,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2911,7 +2920,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2925,7 +2934,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2939,7 +2948,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2953,7 +2962,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2967,7 +2976,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2981,7 +2990,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,10 +3001,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3009,7 +3018,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3023,7 +3032,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3037,7 +3046,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3051,7 +3060,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3065,7 +3074,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3079,7 +3088,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,10 +3099,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3107,7 +3116,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3118,10 +3127,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3135,7 +3144,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,10 +3155,10 @@
         <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,10 +3169,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3177,7 +3186,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3191,7 +3200,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3205,7 +3214,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3219,7 +3228,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3233,7 +3242,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3247,7 +3256,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3261,7 +3270,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3275,7 +3284,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3289,7 +3298,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3303,7 +3312,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3317,7 +3326,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3331,7 +3340,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3345,7 +3354,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3359,7 +3368,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3373,7 +3382,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3387,7 +3396,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3401,7 +3410,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3415,7 +3424,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3429,7 +3438,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3443,7 +3452,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3457,7 +3466,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3471,7 +3480,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3485,7 +3494,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3499,7 +3508,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3513,7 +3522,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3527,7 +3536,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,10 +3547,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3555,7 +3564,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3569,7 +3578,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3583,7 +3592,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,10 +3603,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3611,7 +3620,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3625,7 +3634,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3639,7 +3648,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,7 +3662,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3667,7 +3676,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3681,7 +3690,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3695,7 +3704,7 @@
         <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3709,7 +3718,7 @@
         <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3723,7 +3732,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3737,7 +3746,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3751,7 +3760,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3765,7 +3774,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3779,7 +3788,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3793,7 +3802,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3807,7 +3816,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3821,7 +3830,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3835,7 +3844,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3849,7 +3858,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,10 +3869,10 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3877,7 +3886,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3891,7 +3900,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3905,7 +3914,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,10 +3925,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D142" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3933,7 +3942,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3947,7 +3956,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3961,7 +3970,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3975,7 +3984,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3989,7 +3998,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4003,7 +4012,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4017,7 +4026,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4031,7 +4040,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4045,7 +4054,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,10 +4065,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4073,7 +4082,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4087,7 +4096,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4101,7 +4110,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4115,7 +4124,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,10 +4135,10 @@
         <v>259</v>
       </c>
       <c r="C157" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D157" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4143,7 +4152,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4157,7 +4166,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4171,7 +4180,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4185,7 +4194,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4199,7 +4208,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4213,7 +4222,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4227,7 +4236,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4241,7 +4250,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4255,7 +4264,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4269,7 +4278,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4283,7 +4292,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4297,7 +4306,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4311,7 +4320,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4325,7 +4334,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4339,7 +4348,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4353,7 +4362,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,10 +4373,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D174" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,10 +4387,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,10 +4401,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4409,7 +4418,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4423,7 +4432,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4437,7 +4446,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4451,7 +4460,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4465,7 +4474,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4479,7 +4488,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4493,7 +4502,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,10 +4513,10 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D184" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4521,7 +4530,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4535,7 +4544,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4549,7 +4558,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4563,7 +4572,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4577,7 +4586,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4588,10 +4597,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,10 +4611,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D191" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4619,7 +4628,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,10 +4639,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D193" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,10 +4653,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4661,7 +4670,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,10 +4681,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,10 +4695,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4703,7 +4712,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4717,7 +4726,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,10 +4737,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4745,7 +4754,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,10 +4765,10 @@
         <v>259</v>
       </c>
       <c r="C202" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4773,7 +4782,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4787,7 +4796,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4801,7 +4810,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4815,7 +4824,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,10 +4835,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4843,7 +4852,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,10 +4863,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,10 +4877,10 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4885,7 +4894,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4899,7 +4908,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4913,7 +4922,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4927,7 +4936,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4941,7 +4950,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4955,7 +4964,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4969,7 +4978,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4983,7 +4992,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4997,7 +5006,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5011,7 +5020,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5025,7 +5034,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5039,7 +5048,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5053,7 +5062,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5067,7 +5076,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5081,7 +5090,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,10 +5101,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5109,7 +5118,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5123,7 +5132,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5137,7 +5146,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5151,7 +5160,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5165,7 +5174,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,10 +5185,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D232" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5193,7 +5202,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5207,7 +5216,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5221,7 +5230,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5235,7 +5244,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5249,7 +5258,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5263,7 +5272,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5277,7 +5286,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5291,7 +5300,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5305,7 +5314,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5319,7 +5328,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5333,7 +5342,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5347,7 +5356,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5361,7 +5370,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5375,7 +5384,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5389,7 +5398,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5403,7 +5412,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5417,7 +5426,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5431,7 +5440,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5442,10 +5451,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5459,7 +5468,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5473,7 +5482,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5487,7 +5496,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5501,7 +5510,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5515,7 +5524,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
